--- a/LosBichos/ventas.xlsx
+++ b/LosBichos/ventas.xlsx
@@ -41,7 +41,7 @@
     <t>Hamlet - Teatro</t>
   </si>
   <si>
-    <t>2026-05-19T18:59:39.948690600</t>
+    <t>2026-05-20T08:14:30.905117200</t>
   </si>
   <si>
     <t>120000.0</t>
@@ -59,7 +59,7 @@
     <t>Ferxxo en concierto</t>
   </si>
   <si>
-    <t>2026-05-19T18:59:39.941176600</t>
+    <t>2026-05-20T08:14:30.899113300</t>
   </si>
   <si>
     <t>250000.0</t>
@@ -71,16 +71,16 @@
     <t>C004</t>
   </si>
   <si>
-    <t>2026-05-19T18:59:39.957659900</t>
+    <t>2026-05-20T08:14:30.910116900</t>
+  </si>
+  <si>
+    <t>CREADA</t>
   </si>
   <si>
     <t>C003</t>
   </si>
   <si>
     <t>90000.0</t>
-  </si>
-  <si>
-    <t>CREADA</t>
   </si>
 </sst>
 </file>
@@ -205,12 +205,12 @@
         <v>16</v>
       </c>
       <c r="F4" t="s" s="0">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>13</v>
@@ -222,10 +222,10 @@
         <v>9</v>
       </c>
       <c r="E5" t="s" s="0">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/LosBichos/ventas.xlsx
+++ b/LosBichos/ventas.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="27">
   <si>
     <t>ID Compra</t>
   </si>
@@ -38,49 +38,61 @@
     <t>María Gómez</t>
   </si>
   <si>
+    <t>Feid - Ferxxo en Armenia</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:29:24.947823</t>
+  </si>
+  <si>
+    <t>185000.0</t>
+  </si>
+  <si>
+    <t>PAGADA</t>
+  </si>
+  <si>
+    <t>C001</t>
+  </si>
+  <si>
+    <t>Juan Pérez</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:29:24.935589200</t>
+  </si>
+  <si>
+    <t>345000.0</t>
+  </si>
+  <si>
+    <t>C005</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:29:24.949820</t>
+  </si>
+  <si>
+    <t>60000.0</t>
+  </si>
+  <si>
+    <t>CANCELADA</t>
+  </si>
+  <si>
+    <t>C004</t>
+  </si>
+  <si>
+    <t>2026-05-20T08:29:24.960038300</t>
+  </si>
+  <si>
+    <t>280000.0</t>
+  </si>
+  <si>
+    <t>CREADA</t>
+  </si>
+  <si>
+    <t>C003</t>
+  </si>
+  <si>
     <t>Hamlet - Teatro</t>
   </si>
   <si>
-    <t>2026-05-20T08:14:30.905117200</t>
-  </si>
-  <si>
-    <t>120000.0</t>
-  </si>
-  <si>
-    <t>CANCELADA</t>
-  </si>
-  <si>
-    <t>C001</t>
-  </si>
-  <si>
-    <t>Juan Pérez</t>
-  </si>
-  <si>
-    <t>Ferxxo en concierto</t>
-  </si>
-  <si>
-    <t>2026-05-20T08:14:30.899113300</t>
-  </si>
-  <si>
-    <t>250000.0</t>
-  </si>
-  <si>
-    <t>PAGADA</t>
-  </si>
-  <si>
-    <t>C004</t>
-  </si>
-  <si>
-    <t>2026-05-20T08:14:30.910116900</t>
-  </si>
-  <si>
-    <t>CREADA</t>
-  </si>
-  <si>
-    <t>C003</t>
-  </si>
-  <si>
-    <t>90000.0</t>
+    <t>110000.0</t>
   </si>
 </sst>
 </file>
@@ -125,7 +137,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -176,41 +188,41 @@
         <v>13</v>
       </c>
       <c r="C3" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D3" t="s" s="0">
         <v>14</v>
       </c>
-      <c r="D3" t="s" s="0">
+      <c r="E3" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="E3" t="s" s="0">
-        <v>16</v>
-      </c>
       <c r="F3" t="s" s="0">
-        <v>17</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="0">
         <v>18</v>
       </c>
-      <c r="B4" t="s" s="0">
-        <v>13</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>14</v>
-      </c>
-      <c r="D4" t="s" s="0">
+      <c r="F4" t="s" s="0">
         <v>19</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>16</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>20</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s" s="0">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5" t="s" s="0">
         <v>13</v>
@@ -219,13 +231,33 @@
         <v>8</v>
       </c>
       <c r="D5" t="s" s="0">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="E5" t="s" s="0">
         <v>22</v>
       </c>
       <c r="F5" t="s" s="0">
-        <v>20</v>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="D6" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
